--- a/artfynd/A 52153-2020 artfynd.xlsx
+++ b/artfynd/A 52153-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52153-2020 artfynd.xlsx
+++ b/artfynd/A 52153-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2561,7 +2561,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112606304</v>
+        <v>112610270</v>
       </c>
       <c r="B18" t="n">
         <v>77856</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>755757</v>
+        <v>755752</v>
       </c>
       <c r="R18" t="n">
-        <v>7139135</v>
+        <v>7139125</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112606303</v>
+        <v>112610271</v>
       </c>
       <c r="B19" t="n">
-        <v>77856</v>
+        <v>89771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,21 +2684,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>755735</v>
+        <v>755746</v>
       </c>
       <c r="R19" t="n">
-        <v>7139161</v>
+        <v>7139125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112606302</v>
+        <v>104159590</v>
       </c>
       <c r="B20" t="n">
-        <v>77856</v>
+        <v>77506</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>755735</v>
+        <v>755803.5100043941</v>
       </c>
       <c r="R20" t="n">
-        <v>7139171</v>
+        <v>7139205.292802372</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2848,14 +2848,24 @@
           <t>2022-10-07</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112606305</v>
+        <v>104159591</v>
       </c>
       <c r="B21" t="n">
-        <v>89771</v>
+        <v>77506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,21 +2908,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2922,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>755745</v>
+        <v>755794.8691895118</v>
       </c>
       <c r="R21" t="n">
-        <v>7139125</v>
+        <v>7139177.961474049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2955,14 +2965,24 @@
           <t>2022-10-07</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,1417 +3006,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>112606296</v>
-      </c>
-      <c r="B22" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>755704</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7139356</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>112606297</v>
-      </c>
-      <c r="B23" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>755693</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7139361</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>112606298</v>
-      </c>
-      <c r="B24" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>755743</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7139312</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>112606306</v>
-      </c>
-      <c r="B25" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>755715</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7139136</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>112606295</v>
-      </c>
-      <c r="B26" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>755696</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7139364</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>112606299</v>
-      </c>
-      <c r="B27" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>755716</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7139223</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>112610270</v>
-      </c>
-      <c r="B28" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>755752</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7139125</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>112610271</v>
-      </c>
-      <c r="B29" t="n">
-        <v>89771</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>755746</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7139125</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>112606294</v>
-      </c>
-      <c r="B30" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>755648</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7139389</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>104159590</v>
-      </c>
-      <c r="B31" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>755803.5100043941</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7139205.292802372</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>104159591</v>
-      </c>
-      <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>755794.8691895118</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7139177.961474049</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>112606300</v>
-      </c>
-      <c r="B33" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>755804</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7139205</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>112606301</v>
-      </c>
-      <c r="B34" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Botsmark, Vb</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>755795</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7139178</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
